--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2142.93</v>
+        <v>2163.28</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>40049.63</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6874.55</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17256.2</v>
+        <v>17420.11</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2792.79</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2628.44</v>
+        <v>2638.7</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20782.62</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13264.39</v>
+        <v>13397.22</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>404.95</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4124.73</v>
+        <v>4166.03</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>29002.01</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13958.77</v>
+        <v>14098.55</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12825.33</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>97.75</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>48107.72</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1879.22</v>
+        <v>1888.8</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>857.17</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10430.41</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27326.34</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12352.71</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8571.700000000001</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25715.11</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>37586.6</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>429.66</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>19205.77</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46016.52</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3759.52</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13963.93</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3510.32</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>214.83</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>193131.89</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>9667.34</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4833.67</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12245.28</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>32224.45</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16112.23</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14286.17</v>
+        <v>14241.05</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5155.91</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>64448.86</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6015.23</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>47933.88</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>144.53</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5152.57</v>
+        <v>5142.24</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>18153.11</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.67</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>46725.46</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7218.28</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9357.610000000001</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>526.33</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10182.93</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>44061.57</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1074.15</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9183.969999999999</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7680.67</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1826.05</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>212.68</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6586.68</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11278.56</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>43412.78</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>16477.44</v>
+        <v>16587.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PATRICIO OSVALDO</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PATRICIO OSVALDO</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Region de la Araucania</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Hugo Pascual Paco Bolaños</t>
+          <t>HUGO PASCUAL PACO BOLAÑOS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>76.735.787-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1310,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1375,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1490,7 +1514,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,43 +1539,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>861.54</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>4886-60-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,32 +1599,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1634,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10483.56</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2409-608-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,53 +1655,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5391.65</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2791-98-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1720,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1730,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1760,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27432.71</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2409-646-CM26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,53 +1781,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12400.79</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1856,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1886,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8605.07</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057536-1747-CM26</t>
+          <t>2791-98-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,37 +1907,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1947,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25584.85</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057536-1856-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,37 +1968,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2008,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>37396.2</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2029,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,37 +2039,41 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>427.48</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="27">
@@ -2087,7 +2127,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2100,7 +2144,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1057536-1747-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,37 +2159,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2199,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46114.6</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1057536-1856-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,37 +2220,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2260,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3767.53</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2281,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2291,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2321,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13993.69</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2467-824-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,27 +2352,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2382,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3517.8</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5485-481-CM26</t>
+          <t>2467-824-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,37 +2403,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2443,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>216.23</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2464,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2474,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2504,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>194424.62</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,37 +2525,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2565,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>5485-481-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,53 +2586,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4866.02</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2651,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,43 +2661,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12330.98</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,37 +2716,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2756,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>32122.67</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2777,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,43 +2787,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16061.33</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2424-948-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,37 +2842,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.196.907-0</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2882,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14241.05</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2913,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5139.63</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2968,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3008,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>64308.63</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>748-58-CM26</t>
+          <t>2424-948-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3029,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +3039,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>77.196.907-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3069,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6002.14</v>
+        <v>14241.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>748-59-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,37 +3090,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3130,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1275.46</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>3894-54-SE26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3151,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,43 +3161,47 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>47837.79</v>
+        <v>12849.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,37 +3216,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3256,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>144.24</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3134-146-CM26</t>
+          <t>748-58-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,37 +3277,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3317,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5142.24</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>748-59-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,37 +3338,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3378,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>18116.72</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4887-85-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3409,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.978.390-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1275.67</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2416-187-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,27 +3474,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3504,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>46631.79</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,32 +3530,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3565,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7203.81</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,37 +3586,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3626,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2467-871-CM26</t>
+          <t>4887-85-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3647,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3657,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.978.390-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3687,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>517.84</v>
+        <v>1275.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>2416-187-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3708,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3718,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3748,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10018.6</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2416-186-CM26</t>
+          <t>3134-146-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3769,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,43 +3779,47 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.854.171-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>43355.11</v>
+        <v>5142.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5952-97-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3834,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3844,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3859,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>HUGO PASCUAL PACO BOLAÑOS</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>10.472.608-9</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3874,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1061.65</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>2467-871-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3895,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,27 +3905,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3935,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9133.049999999999</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3956,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,27 +3966,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3996,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7638.09</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>2416-186-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +4017,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,27 +4027,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +4057,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1817.07</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>5952-97-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,37 +4078,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>HUGO PASCUAL PACO BOLAÑOS</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>10.472.608-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4118,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>211.64</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2793-734-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4139,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4149,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4179,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6554.29</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4200,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4210,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,28 +4225,32 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11354.05</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4265,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4275,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4305,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>43703.37</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2102-655-CM26</t>
+          <t>4886-97-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4326,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4351,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.343.454-0</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,6 +4366,254 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
+        <v>211.64</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2793-734-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>6554.29</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1549-3384-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>11354.05</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1057417-14563-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>43703.37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2102-655-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.602.212-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Transportes Myriam y Sergio Ltda.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.343.454-0</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>16587.73</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -1940,7 +1940,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -623,7 +623,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -812,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1060,7 +1064,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1312,7 +1316,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2133,7 +2137,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2625,7 +2629,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2690,7 +2694,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4487,7 +4491,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4550,7 +4554,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1518,7 +1518,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2735-850-SE26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>82539.53</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="19">
@@ -1644,7 +1644,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2735-849-SE26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38722.38</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1729,48 +1729,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10483.56</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2735-872-SE26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1795,41 +1799,37 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.070.302-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28920.36</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="23">
@@ -2087,7 +2087,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1057536-1747-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2127,32 +2127,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.384.260-6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>19108.48</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057536-1747-CM26</t>
+          <t>1057536-1856-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2207,13 +2203,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>25584.85</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057536-1856-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2238,27 +2234,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2268,13 +2264,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37396.2</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2294,48 +2290,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>JOSUE MANUEL</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>76.370.023-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>427.48</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2360,27 +2360,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>13993.69</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2467-824-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2416,32 +2416,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3517.8</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>46114.6</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>2467-824-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2543,27 +2543,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3767.53</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="35">
@@ -2644,7 +2644,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>5965-193-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2669,47 +2669,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>194424.62</v>
+        <v>656.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2729,48 +2725,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2790,52 +2790,48 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4866.02</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2850,53 +2846,57 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12330.98</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2911,57 +2911,53 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32122.67</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2986,43 +2982,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16061.33</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2424-948-CM26</t>
+          <t>3894-54-SE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3042,48 +3042,52 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.196.907-0</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>14241.05</v>
+        <v>12849.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3103,32 +3107,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3138,13 +3142,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5139.63</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3894-54-SE26</t>
+          <t>2424-948-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3164,52 +3168,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>77.196.907-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12849.07</v>
+        <v>14241.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3234,27 +3234,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3264,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>64308.63</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>748-58-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>6002.14</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>748-59-CM26</t>
+          <t>748-58-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1275.46</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>748-59-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3407,57 +3407,53 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.845.503-1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>18116.72</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3477,32 +3473,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3512,13 +3508,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>144.24</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3543,27 +3539,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3573,13 +3569,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>47837.79</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3599,48 +3595,52 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7203.81</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4887-85-CM26</t>
+          <t>3134-146-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3665,43 +3665,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.978.390-5</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.854.171-8</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1275.67</v>
+        <v>5142.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2416-187-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3721,32 +3725,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3756,13 +3760,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>46631.79</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3134-146-CM26</t>
+          <t>4887-85-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3787,47 +3791,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.978.390-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
+          <t>15.552.949-0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5142.24</v>
+        <v>1275.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>2416-187-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3842,37 +3842,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2467-871-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,37 +3903,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>517.84</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>2467-871-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3974,27 +3974,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10018.6</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2416-186-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4035,27 +4035,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4065,13 +4065,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>43355.11</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5952-97-CM26</t>
+          <t>2416-186-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4086,37 +4086,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HUGO PASCUAL PACO BOLAÑOS</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>10.472.608-9</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1061.65</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>5952-97-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4157,27 +4157,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>HUGO PASCUAL PACO BOLAÑOS</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>10.472.608-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4187,13 +4187,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9133.049999999999</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,47 +4218,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7638.09</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4273,7 +4269,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4283,43 +4279,47 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1817.07</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,32 +4339,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>211.64</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2793-734-CM26</t>
+          <t>4886-97-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6554.29</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>2793-734-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4481,26 +4481,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11354.05</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="66">
@@ -4526,7 +4522,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4571,61 +4567,126 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>1549-3384-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>11354.05</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>2102-655-CM26</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>61.602.212-1</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>76.343.454-0</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="n">
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
         <v>16587.73</v>
       </c>
     </row>
